--- a/data/translations.wikidata.xlsx
+++ b/data/translations.wikidata.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -34,16 +34,28 @@
     <t xml:space="preserve">English</t>
   </si>
   <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">de</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">en</t>
+  </si>
+  <si>
     <t xml:space="preserve">filter_ref</t>
   </si>
   <si>
-    <t xml:space="preserve">Normdatenbank</t>
+    <t xml:space="preserve">Datenbank</t>
   </si>
   <si>
     <t xml:space="preserve">refs</t>
   </si>
   <si>
-    <t xml:space="preserve">Normdatenbanken</t>
+    <t xml:space="preserve">Datenbanken</t>
   </si>
   <si>
     <t xml:space="preserve">or</t>
@@ -68,6 +80,36 @@
   </si>
   <si>
     <t xml:space="preserve">Wikdata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">results</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">result</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resultat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">search_prompt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freitextsuche Namen oder Nummer des Wikidata Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auswahl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nicht referenziert</t>
   </si>
 </sst>
 </file>
@@ -209,48 +251,101 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="1048505" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048507" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048508" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>

--- a/data/translations.wikidata.xlsx
+++ b/data/translations.wikidata.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="38">
   <si>
     <t xml:space="preserve">key</t>
   </si>
@@ -43,21 +43,24 @@
     <t xml:space="preserve">fr</t>
   </si>
   <si>
-    <t xml:space="preserve">en</t>
-  </si>
-  <si>
     <t xml:space="preserve">filter_ref</t>
   </si>
   <si>
     <t xml:space="preserve">Datenbank</t>
   </si>
   <si>
+    <t xml:space="preserve">base de données</t>
+  </si>
+  <si>
     <t xml:space="preserve">refs</t>
   </si>
   <si>
     <t xml:space="preserve">Datenbanken</t>
   </si>
   <si>
+    <t xml:space="preserve">bases de données</t>
+  </si>
+  <si>
     <t xml:space="preserve">or</t>
   </si>
   <si>
@@ -73,13 +76,46 @@
     <t xml:space="preserve">dfkv</t>
   </si>
   <si>
-    <t xml:space="preserve">DFKV</t>
+    <t xml:space="preserve">Deutsch-französische Kunstvermittlung von 1870-1960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La réception artistique franco-allemande de 1870-1960 </t>
   </si>
   <si>
     <t xml:space="preserve">wikidata</t>
   </si>
   <si>
-    <t xml:space="preserve">Wikdata</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Wik</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF4500"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">data</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Wikidata</t>
   </si>
   <si>
     <t xml:space="preserve">results</t>
@@ -88,16 +124,52 @@
     <t xml:space="preserve">Resultate</t>
   </si>
   <si>
+    <t xml:space="preserve">résultats trouvés</t>
+  </si>
+  <si>
     <t xml:space="preserve">result</t>
   </si>
   <si>
     <t xml:space="preserve">Resultat</t>
   </si>
   <si>
+    <t xml:space="preserve">résultat trouvé</t>
+  </si>
+  <si>
     <t xml:space="preserve">search_prompt</t>
   </si>
   <si>
-    <t xml:space="preserve">Freitextsuche Namen oder Nummer des Wikidata Items</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Freitextsuche</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF1493"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Namen oder Nummer des Wikidata Items</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche plein texte d’un nom ou du numéro d’un élément Wikidata</t>
   </si>
   <si>
     <t xml:space="preserve">selection</t>
@@ -106,10 +178,16 @@
     <t xml:space="preserve">Auswahl</t>
   </si>
   <si>
+    <t xml:space="preserve">Votre sélection</t>
+  </si>
+  <si>
     <t xml:space="preserve">no_reference</t>
   </si>
   <si>
     <t xml:space="preserve">nicht referenziert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non référencé</t>
   </si>
 </sst>
 </file>
@@ -119,7 +197,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -148,13 +226,33 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF1493"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF4500"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7FFF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -191,7 +289,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,6 +300,26 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -213,6 +331,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF1493"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF7FFF00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF4500"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -254,15 +432,15 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -273,77 +451,107 @@
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
+      <c r="A8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="1048506" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
